--- a/ksoft/docs/fields_details/jalmeida/CE0302.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302.xlsx
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2B77C8-4486-495E-B5CD-DE5168B9EDAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{465D843A-85D6-4039-88D3-9F8F77803BD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF90C4D-28AB-4091-8FD6-2195F76D9102}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33815CE0-F2A6-4091-8A92-7C6B1824D0BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21C001C-6D32-45DC-B86B-02FF559AFE54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED627E8B-4785-4A7B-9C1B-E5AAE5497A2D}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/CE0302.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302.xlsx
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{465D843A-85D6-4039-88D3-9F8F77803BD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2B77C8-4486-495E-B5CD-DE5168B9EDAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33815CE0-F2A6-4091-8A92-7C6B1824D0BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF90C4D-28AB-4091-8FD6-2195F76D9102}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED627E8B-4785-4A7B-9C1B-E5AAE5497A2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21C001C-6D32-45DC-B86B-02FF559AFE54}"/>
 </file>